--- a/nr-update-system-nss/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/nr-update-system-nss/ig/StructureDefinition-fr-core-patient.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5343" uniqueCount="695">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5677" uniqueCount="709">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-22T17:34:51+00:00</t>
+    <t>2026-02-23T07:43:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1008,28 +1008,28 @@
     <t>CX.4 / (CX.4,CX.9,CX.10)</t>
   </si>
   <si>
-    <t>Patient.identifier:NSS</t>
-  </si>
-  <si>
-    <t>NSS</t>
+    <t>Patient.identifier:NSS-NIR</t>
+  </si>
+  <si>
+    <t>NSS-NIR</t>
   </si>
   <si>
     <t>National Health Plan Identifier | Le Numéro d'Inscription au Répertoire (NIR) de facturation permet de faire transiter le numéro de sécurité social de l’ayant droit ou du bénéfiaire (patient) / le numéro de sécurité sociale de l’ouvrant droit (assuré).</t>
   </si>
   <si>
-    <t>Patient.identifier:NSS.id</t>
-  </si>
-  <si>
-    <t>Patient.identifier:NSS.extension</t>
-  </si>
-  <si>
-    <t>Patient.identifier:NSS.use</t>
+    <t>Patient.identifier:NSS-NIR.id</t>
+  </si>
+  <si>
+    <t>Patient.identifier:NSS-NIR.extension</t>
+  </si>
+  <si>
+    <t>Patient.identifier:NSS-NIR.use</t>
   </si>
   <si>
     <t>official</t>
   </si>
   <si>
-    <t>Patient.identifier:NSS.type</t>
+    <t>Patient.identifier:NSS-NIR.type</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
@@ -1040,19 +1040,61 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>Patient.identifier:NSS.system</t>
+    <t>Patient.identifier:NSS-NIR.system</t>
+  </si>
+  <si>
+    <t>Autorité d’affectation du NIR utilisé en tant que numéro de sécurité sociale</t>
   </si>
   <si>
     <t>urn:oid:1.2.250.1.213.1.4.13</t>
   </si>
   <si>
-    <t>Patient.identifier:NSS.value</t>
-  </si>
-  <si>
-    <t>Patient.identifier:NSS.period</t>
-  </si>
-  <si>
-    <t>Patient.identifier:NSS.assigner</t>
+    <t>Patient.identifier:NSS-NIR.value</t>
+  </si>
+  <si>
+    <t>Patient.identifier:NSS-NIR.period</t>
+  </si>
+  <si>
+    <t>Patient.identifier:NSS-NIR.assigner</t>
+  </si>
+  <si>
+    <t>Patient.identifier:NSS-NIA</t>
+  </si>
+  <si>
+    <t>NSS-NIA</t>
+  </si>
+  <si>
+    <t>National Health Plan Identifier | Le Numéro d'Inscription au Répertoire (NIA) de facturation d'attente permet de faire transiter le numéro de sécurité social de l’ayant droit ou du bénéfiaire (patient) / le numéro de sécurité sociale d'attente de l’ouvrant droit (assuré).</t>
+  </si>
+  <si>
+    <t>Patient.identifier:NSS-NIA.id</t>
+  </si>
+  <si>
+    <t>Patient.identifier:NSS-NIA.extension</t>
+  </si>
+  <si>
+    <t>Patient.identifier:NSS-NIA.use</t>
+  </si>
+  <si>
+    <t>Patient.identifier:NSS-NIA.type</t>
+  </si>
+  <si>
+    <t>Patient.identifier:NSS-NIA.system</t>
+  </si>
+  <si>
+    <t>Autorité d’affectation du NIA utilisé en tant que numéro de sécurité sociale</t>
+  </si>
+  <si>
+    <t>urn:oid:1.2.250.1.213.1.4.14</t>
+  </si>
+  <si>
+    <t>Patient.identifier:NSS-NIA.value</t>
+  </si>
+  <si>
+    <t>Patient.identifier:NSS-NIA.period</t>
+  </si>
+  <si>
+    <t>Patient.identifier:NSS-NIA.assigner</t>
   </si>
   <si>
     <t>Patient.identifier:INS-C</t>
@@ -2515,7 +2557,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO143"/>
+  <dimension ref="A1:AO152"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="46.9765625" customWidth="true" bestFit="true"/>
@@ -7620,7 +7662,7 @@
         <v>132</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>286</v>
+        <v>327</v>
       </c>
       <c r="M44" t="s" s="2">
         <v>287</v>
@@ -7639,7 +7681,7 @@
         <v>82</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="T44" t="s" s="2">
         <v>290</v>
@@ -7710,7 +7752,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B45" t="s" s="2">
         <v>294</v>
@@ -7827,7 +7869,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B46" t="s" s="2">
         <v>302</v>
@@ -7942,7 +7984,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B47" t="s" s="2">
         <v>309</v>
@@ -8059,13 +8101,13 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B48" t="s" s="2">
         <v>253</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D48" t="s" s="2">
         <v>82</v>
@@ -8075,7 +8117,7 @@
         <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>82</v>
@@ -8090,7 +8132,7 @@
         <v>254</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M48" t="s" s="2">
         <v>256</v>
@@ -8178,7 +8220,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B49" t="s" s="2">
         <v>264</v>
@@ -8293,7 +8335,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B50" t="s" s="2">
         <v>265</v>
@@ -8410,7 +8452,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B51" t="s" s="2">
         <v>266</v>
@@ -8458,7 +8500,7 @@
         <v>82</v>
       </c>
       <c r="S51" t="s" s="2">
-        <v>337</v>
+        <v>323</v>
       </c>
       <c r="T51" t="s" s="2">
         <v>82</v>
@@ -8577,7 +8619,7 @@
         <v>82</v>
       </c>
       <c r="S52" t="s" s="2">
-        <v>339</v>
+        <v>325</v>
       </c>
       <c r="T52" t="s" s="2">
         <v>82</v>
@@ -8646,7 +8688,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B53" t="s" s="2">
         <v>285</v>
@@ -8675,7 +8717,7 @@
         <v>132</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>286</v>
+        <v>340</v>
       </c>
       <c r="M53" t="s" s="2">
         <v>287</v>
@@ -9130,7 +9172,7 @@
         <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>82</v>
@@ -9513,7 +9555,7 @@
         <v>82</v>
       </c>
       <c r="S60" t="s" s="2">
-        <v>337</v>
+        <v>351</v>
       </c>
       <c r="T60" t="s" s="2">
         <v>82</v>
@@ -9584,7 +9626,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B61" t="s" s="2">
         <v>276</v>
@@ -9632,7 +9674,7 @@
         <v>82</v>
       </c>
       <c r="S61" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="T61" t="s" s="2">
         <v>82</v>
@@ -9701,7 +9743,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B62" t="s" s="2">
         <v>285</v>
@@ -9749,7 +9791,7 @@
         <v>82</v>
       </c>
       <c r="S62" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="T62" t="s" s="2">
         <v>290</v>
@@ -9820,7 +9862,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B63" t="s" s="2">
         <v>294</v>
@@ -9937,7 +9979,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B64" t="s" s="2">
         <v>302</v>
@@ -10052,7 +10094,7 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B65" t="s" s="2">
         <v>309</v>
@@ -10169,13 +10211,13 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B66" t="s" s="2">
         <v>253</v>
       </c>
       <c r="C66" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D66" t="s" s="2">
         <v>82</v>
@@ -10185,7 +10227,7 @@
         <v>80</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>82</v>
@@ -10200,7 +10242,7 @@
         <v>254</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M66" t="s" s="2">
         <v>256</v>
@@ -10288,7 +10330,7 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B67" t="s" s="2">
         <v>264</v>
@@ -10403,7 +10445,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B68" t="s" s="2">
         <v>265</v>
@@ -10520,7 +10562,7 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B69" t="s" s="2">
         <v>266</v>
@@ -10555,7 +10597,7 @@
         <v>268</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>364</v>
+        <v>269</v>
       </c>
       <c r="O69" t="s" s="2">
         <v>270</v>
@@ -10568,7 +10610,7 @@
         <v>82</v>
       </c>
       <c r="S69" t="s" s="2">
-        <v>82</v>
+        <v>351</v>
       </c>
       <c r="T69" t="s" s="2">
         <v>82</v>
@@ -10585,9 +10627,11 @@
       <c r="X69" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="Y69" s="2"/>
+      <c r="Y69" t="s" s="2">
+        <v>272</v>
+      </c>
       <c r="Z69" t="s" s="2">
-        <v>365</v>
+        <v>273</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>82</v>
@@ -10637,7 +10681,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B70" t="s" s="2">
         <v>276</v>
@@ -10685,7 +10729,7 @@
         <v>82</v>
       </c>
       <c r="S70" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="T70" t="s" s="2">
         <v>82</v>
@@ -10754,7 +10798,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B71" t="s" s="2">
         <v>285</v>
@@ -10802,7 +10846,7 @@
         <v>82</v>
       </c>
       <c r="S71" t="s" s="2">
-        <v>82</v>
+        <v>368</v>
       </c>
       <c r="T71" t="s" s="2">
         <v>290</v>
@@ -11608,7 +11652,7 @@
         <v>268</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>269</v>
+        <v>378</v>
       </c>
       <c r="O78" t="s" s="2">
         <v>270</v>
@@ -11621,7 +11665,7 @@
         <v>82</v>
       </c>
       <c r="S78" t="s" s="2">
-        <v>337</v>
+        <v>82</v>
       </c>
       <c r="T78" t="s" s="2">
         <v>82</v>
@@ -11638,11 +11682,9 @@
       <c r="X78" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="Y78" t="s" s="2">
-        <v>272</v>
-      </c>
+      <c r="Y78" s="2"/>
       <c r="Z78" t="s" s="2">
-        <v>273</v>
+        <v>379</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>82</v>
@@ -11692,7 +11734,7 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B79" t="s" s="2">
         <v>276</v>
@@ -11740,7 +11782,7 @@
         <v>82</v>
       </c>
       <c r="S79" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="T79" t="s" s="2">
         <v>82</v>
@@ -11809,7 +11851,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B80" t="s" s="2">
         <v>285</v>
@@ -11928,7 +11970,7 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B81" t="s" s="2">
         <v>294</v>
@@ -12045,7 +12087,7 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B82" t="s" s="2">
         <v>302</v>
@@ -12160,7 +12202,7 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B83" t="s" s="2">
         <v>309</v>
@@ -12277,12 +12319,14 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="C84" s="2"/>
+        <v>253</v>
+      </c>
+      <c r="C84" t="s" s="2">
+        <v>387</v>
+      </c>
       <c r="D84" t="s" s="2">
         <v>82</v>
       </c>
@@ -12291,38 +12335,34 @@
         <v>80</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I84" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J84" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>385</v>
+        <v>254</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>388</v>
-      </c>
+        <v>256</v>
+      </c>
+      <c r="N84" s="2"/>
       <c r="O84" t="s" s="2">
-        <v>389</v>
+        <v>257</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q84" t="s" s="2">
-        <v>390</v>
-      </c>
+      <c r="Q84" s="2"/>
       <c r="R84" t="s" s="2">
         <v>82</v>
       </c>
@@ -12366,13 +12406,13 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>384</v>
+        <v>253</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>82</v>
@@ -12381,16 +12421,16 @@
         <v>102</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>391</v>
+        <v>260</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>108</v>
+        <v>261</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>392</v>
+        <v>262</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>82</v>
+        <v>263</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>82</v>
@@ -12398,10 +12438,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>393</v>
+        <v>264</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12412,7 +12452,7 @@
         <v>80</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>82</v>
@@ -12421,23 +12461,19 @@
         <v>82</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>394</v>
+        <v>104</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>395</v>
+        <v>105</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="O85" t="s" s="2">
-        <v>398</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N85" s="2"/>
+      <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>82</v>
       </c>
@@ -12473,41 +12509,43 @@
         <v>82</v>
       </c>
       <c r="AB85" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="AC85" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE85" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>393</v>
+        <v>107</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>400</v>
+        <v>108</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>401</v>
+        <v>82</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>402</v>
+        <v>82</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>82</v>
@@ -12515,16 +12553,14 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>403</v>
+        <v>390</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="C86" t="s" s="2">
-        <v>404</v>
-      </c>
+        <v>265</v>
+      </c>
+      <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
@@ -12540,23 +12576,21 @@
         <v>82</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>405</v>
+        <v>111</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>406</v>
+        <v>112</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>407</v>
+        <v>113</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>398</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>82</v>
       </c>
@@ -12592,19 +12626,19 @@
         <v>82</v>
       </c>
       <c r="AB86" t="s" s="2">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="AC86" t="s" s="2">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="AD86" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE86" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>393</v>
+        <v>118</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12616,19 +12650,19 @@
         <v>82</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>400</v>
+        <v>108</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>401</v>
+        <v>82</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>402</v>
+        <v>82</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>82</v>
@@ -12636,10 +12670,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>408</v>
+        <v>391</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>409</v>
+        <v>266</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12647,7 +12681,7 @@
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G87" t="s" s="2">
         <v>90</v>
@@ -12656,22 +12690,26 @@
         <v>82</v>
       </c>
       <c r="I87" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>104</v>
+        <v>171</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>105</v>
+        <v>267</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N87" s="2"/>
-      <c r="O87" s="2"/>
+        <v>268</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="O87" t="s" s="2">
+        <v>270</v>
+      </c>
       <c r="P87" t="s" s="2">
         <v>82</v>
       </c>
@@ -12680,7 +12718,7 @@
         <v>82</v>
       </c>
       <c r="S87" t="s" s="2">
-        <v>82</v>
+        <v>351</v>
       </c>
       <c r="T87" t="s" s="2">
         <v>82</v>
@@ -12695,13 +12733,13 @@
         <v>82</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>82</v>
+        <v>271</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>82</v>
+        <v>272</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>82</v>
+        <v>273</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>82</v>
@@ -12719,7 +12757,7 @@
         <v>82</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>107</v>
+        <v>274</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -12731,10 +12769,10 @@
         <v>82</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>108</v>
+        <v>275</v>
       </c>
       <c r="AL87" t="s" s="2">
         <v>82</v>
@@ -12743,7 +12781,7 @@
         <v>82</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>82</v>
+        <v>194</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>82</v>
@@ -12751,21 +12789,21 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>410</v>
+        <v>392</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>411</v>
+        <v>276</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>82</v>
@@ -12774,21 +12812,23 @@
         <v>82</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>111</v>
+        <v>277</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>112</v>
+        <v>278</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>113</v>
+        <v>279</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O88" s="2"/>
+        <v>280</v>
+      </c>
+      <c r="O88" t="s" s="2">
+        <v>281</v>
+      </c>
       <c r="P88" t="s" s="2">
         <v>82</v>
       </c>
@@ -12797,7 +12837,7 @@
         <v>82</v>
       </c>
       <c r="S88" t="s" s="2">
-        <v>82</v>
+        <v>393</v>
       </c>
       <c r="T88" t="s" s="2">
         <v>82</v>
@@ -12812,46 +12852,44 @@
         <v>82</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y88" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="Y88" s="2"/>
       <c r="Z88" t="s" s="2">
-        <v>82</v>
+        <v>282</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB88" t="s" s="2">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="AC88" t="s" s="2">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="AD88" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE88" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>118</v>
+        <v>283</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>108</v>
+        <v>275</v>
       </c>
       <c r="AL88" t="s" s="2">
         <v>82</v>
@@ -12860,7 +12898,7 @@
         <v>82</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>82</v>
+        <v>284</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>82</v>
@@ -12868,10 +12906,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>412</v>
+        <v>394</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>413</v>
+        <v>285</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12888,25 +12926,25 @@
         <v>82</v>
       </c>
       <c r="I89" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J89" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>171</v>
+        <v>132</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>414</v>
+        <v>286</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>415</v>
+        <v>287</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>416</v>
+        <v>288</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>417</v>
+        <v>289</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>82</v>
@@ -12916,10 +12954,10 @@
         <v>82</v>
       </c>
       <c r="S89" t="s" s="2">
-        <v>418</v>
+        <v>82</v>
       </c>
       <c r="T89" t="s" s="2">
-        <v>82</v>
+        <v>290</v>
       </c>
       <c r="U89" t="s" s="2">
         <v>82</v>
@@ -12931,13 +12969,13 @@
         <v>82</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>271</v>
+        <v>82</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>419</v>
+        <v>82</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>420</v>
+        <v>82</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>82</v>
@@ -12955,7 +12993,7 @@
         <v>82</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>421</v>
+        <v>291</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -12970,7 +13008,7 @@
         <v>102</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>422</v>
+        <v>292</v>
       </c>
       <c r="AL89" t="s" s="2">
         <v>82</v>
@@ -12979,7 +13017,7 @@
         <v>82</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>423</v>
+        <v>293</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>82</v>
@@ -12987,10 +13025,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>424</v>
+        <v>395</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>425</v>
+        <v>294</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12998,7 +13036,7 @@
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G90" t="s" s="2">
         <v>90</v>
@@ -13016,17 +13054,15 @@
         <v>104</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>426</v>
+        <v>295</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>427</v>
+        <v>296</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="O90" t="s" s="2">
-        <v>429</v>
-      </c>
+        <v>297</v>
+      </c>
+      <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>82</v>
       </c>
@@ -13038,7 +13074,7 @@
         <v>82</v>
       </c>
       <c r="T90" t="s" s="2">
-        <v>82</v>
+        <v>298</v>
       </c>
       <c r="U90" t="s" s="2">
         <v>82</v>
@@ -13074,7 +13110,7 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>430</v>
+        <v>299</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -13089,7 +13125,7 @@
         <v>102</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>431</v>
+        <v>300</v>
       </c>
       <c r="AL90" t="s" s="2">
         <v>82</v>
@@ -13098,7 +13134,7 @@
         <v>82</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>432</v>
+        <v>301</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>82</v>
@@ -13106,14 +13142,14 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>433</v>
+        <v>396</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>434</v>
+        <v>302</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>435</v>
+        <v>82</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
@@ -13132,17 +13168,15 @@
         <v>91</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>104</v>
+        <v>303</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>436</v>
+        <v>304</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>438</v>
-      </c>
+        <v>305</v>
+      </c>
+      <c r="N91" s="2"/>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>82</v>
@@ -13191,7 +13225,7 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>439</v>
+        <v>306</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13206,7 +13240,7 @@
         <v>102</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>440</v>
+        <v>307</v>
       </c>
       <c r="AL91" t="s" s="2">
         <v>82</v>
@@ -13215,7 +13249,7 @@
         <v>82</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>441</v>
+        <v>308</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>82</v>
@@ -13223,21 +13257,21 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>442</v>
+        <v>397</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>443</v>
+        <v>309</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>444</v>
+        <v>82</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>82</v>
@@ -13249,16 +13283,16 @@
         <v>91</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>104</v>
+        <v>310</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>445</v>
+        <v>311</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>446</v>
+        <v>312</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>447</v>
+        <v>313</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -13308,13 +13342,13 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>448</v>
+        <v>314</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>82</v>
@@ -13323,7 +13357,7 @@
         <v>102</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>449</v>
+        <v>315</v>
       </c>
       <c r="AL92" t="s" s="2">
         <v>82</v>
@@ -13332,7 +13366,7 @@
         <v>82</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>450</v>
+        <v>316</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>82</v>
@@ -13340,10 +13374,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>451</v>
+        <v>398</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>452</v>
+        <v>398</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13354,32 +13388,38 @@
         <v>80</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I93" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="J93" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>104</v>
+        <v>399</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>453</v>
+        <v>400</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="N93" s="2"/>
-      <c r="O93" s="2"/>
+        <v>401</v>
+      </c>
+      <c r="N93" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="O93" t="s" s="2">
+        <v>403</v>
+      </c>
       <c r="P93" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q93" s="2"/>
+      <c r="Q93" t="s" s="2">
+        <v>404</v>
+      </c>
       <c r="R93" t="s" s="2">
         <v>82</v>
       </c>
@@ -13423,13 +13463,13 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>455</v>
+        <v>398</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>82</v>
@@ -13438,16 +13478,16 @@
         <v>102</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>456</v>
+        <v>405</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>82</v>
+        <v>406</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>457</v>
+        <v>82</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>82</v>
@@ -13455,10 +13495,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>458</v>
+        <v>407</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>459</v>
+        <v>407</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13481,16 +13521,20 @@
         <v>91</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>104</v>
+        <v>408</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>460</v>
+        <v>409</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="N94" s="2"/>
-      <c r="O94" s="2"/>
+        <v>410</v>
+      </c>
+      <c r="N94" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="O94" t="s" s="2">
+        <v>412</v>
+      </c>
       <c r="P94" t="s" s="2">
         <v>82</v>
       </c>
@@ -13526,19 +13570,17 @@
         <v>82</v>
       </c>
       <c r="AB94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC94" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>413</v>
+      </c>
+      <c r="AC94" s="2"/>
       <c r="AD94" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE94" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>462</v>
+        <v>407</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13553,16 +13595,16 @@
         <v>102</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>463</v>
+        <v>414</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>82</v>
+        <v>415</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>464</v>
+        <v>416</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>82</v>
@@ -13570,12 +13612,14 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>465</v>
+        <v>417</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="C95" s="2"/>
+        <v>407</v>
+      </c>
+      <c r="C95" t="s" s="2">
+        <v>418</v>
+      </c>
       <c r="D95" t="s" s="2">
         <v>82</v>
       </c>
@@ -13584,7 +13628,7 @@
         <v>80</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>82</v>
@@ -13596,17 +13640,19 @@
         <v>91</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>303</v>
+        <v>419</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>467</v>
+        <v>420</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="N95" s="2"/>
+        <v>421</v>
+      </c>
+      <c r="N95" t="s" s="2">
+        <v>411</v>
+      </c>
       <c r="O95" t="s" s="2">
-        <v>469</v>
+        <v>412</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>82</v>
@@ -13655,13 +13701,13 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>470</v>
+        <v>407</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>82</v>
@@ -13670,16 +13716,16 @@
         <v>102</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>471</v>
+        <v>414</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>82</v>
+        <v>415</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>472</v>
+        <v>416</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>82</v>
@@ -13687,14 +13733,12 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>473</v>
+        <v>422</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="C96" t="s" s="2">
-        <v>474</v>
-      </c>
+        <v>423</v>
+      </c>
+      <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
         <v>82</v>
       </c>
@@ -13703,7 +13747,7 @@
         <v>80</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>82</v>
@@ -13712,23 +13756,19 @@
         <v>82</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>405</v>
+        <v>104</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>475</v>
+        <v>105</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="O96" t="s" s="2">
-        <v>398</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N96" s="2"/>
+      <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>82</v>
       </c>
@@ -13776,31 +13816,31 @@
         <v>82</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>393</v>
+        <v>107</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>400</v>
+        <v>108</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>401</v>
+        <v>82</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>402</v>
+        <v>82</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>82</v>
@@ -13808,21 +13848,21 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>477</v>
+        <v>424</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>409</v>
+        <v>425</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>82</v>
@@ -13834,15 +13874,17 @@
         <v>82</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N97" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N97" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>82</v>
@@ -13879,31 +13921,31 @@
         <v>82</v>
       </c>
       <c r="AB97" t="s" s="2">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="AC97" t="s" s="2">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="AD97" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE97" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>108</v>
@@ -13923,44 +13965,46 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>478</v>
+        <v>426</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>411</v>
+        <v>427</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I98" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>111</v>
+        <v>171</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>112</v>
+        <v>428</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>113</v>
+        <v>429</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O98" s="2"/>
+        <v>430</v>
+      </c>
+      <c r="O98" t="s" s="2">
+        <v>431</v>
+      </c>
       <c r="P98" t="s" s="2">
         <v>82</v>
       </c>
@@ -13969,7 +14013,7 @@
         <v>82</v>
       </c>
       <c r="S98" t="s" s="2">
-        <v>82</v>
+        <v>432</v>
       </c>
       <c r="T98" t="s" s="2">
         <v>82</v>
@@ -13984,46 +14028,46 @@
         <v>82</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>82</v>
+        <v>271</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>82</v>
+        <v>433</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>82</v>
+        <v>434</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB98" t="s" s="2">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="AC98" t="s" s="2">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="AD98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE98" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>118</v>
+        <v>435</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>108</v>
+        <v>436</v>
       </c>
       <c r="AL98" t="s" s="2">
         <v>82</v>
@@ -14032,7 +14076,7 @@
         <v>82</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>82</v>
+        <v>437</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>82</v>
@@ -14040,14 +14084,12 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>479</v>
+        <v>438</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="C99" t="s" s="2">
-        <v>480</v>
-      </c>
+        <v>439</v>
+      </c>
+      <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
         <v>82</v>
       </c>
@@ -14065,19 +14107,23 @@
         <v>82</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>481</v>
+        <v>104</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>482</v>
+        <v>440</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="N99" s="2"/>
-      <c r="O99" s="2"/>
+        <v>441</v>
+      </c>
+      <c r="N99" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="O99" t="s" s="2">
+        <v>443</v>
+      </c>
       <c r="P99" t="s" s="2">
         <v>82</v>
       </c>
@@ -14125,22 +14171,22 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>118</v>
+        <v>444</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>82</v>
+        <v>445</v>
       </c>
       <c r="AL99" t="s" s="2">
         <v>82</v>
@@ -14149,7 +14195,7 @@
         <v>82</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>82</v>
+        <v>446</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>82</v>
@@ -14157,18 +14203,18 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>484</v>
+        <v>447</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>413</v>
+        <v>448</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>82</v>
+        <v>449</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G100" t="s" s="2">
         <v>90</v>
@@ -14177,26 +14223,24 @@
         <v>82</v>
       </c>
       <c r="I100" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J100" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>171</v>
+        <v>104</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>414</v>
+        <v>450</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>415</v>
+        <v>451</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="O100" t="s" s="2">
-        <v>417</v>
-      </c>
+        <v>452</v>
+      </c>
+      <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>82</v>
       </c>
@@ -14205,7 +14249,7 @@
         <v>82</v>
       </c>
       <c r="S100" t="s" s="2">
-        <v>323</v>
+        <v>82</v>
       </c>
       <c r="T100" t="s" s="2">
         <v>82</v>
@@ -14220,13 +14264,13 @@
         <v>82</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>271</v>
+        <v>82</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>419</v>
+        <v>82</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>420</v>
+        <v>82</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>82</v>
@@ -14244,7 +14288,7 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>421</v>
+        <v>453</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14259,7 +14303,7 @@
         <v>102</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>422</v>
+        <v>454</v>
       </c>
       <c r="AL100" t="s" s="2">
         <v>82</v>
@@ -14268,7 +14312,7 @@
         <v>82</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>423</v>
+        <v>455</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>82</v>
@@ -14276,21 +14320,21 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>485</v>
+        <v>456</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>425</v>
+        <v>457</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>82</v>
+        <v>458</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>82</v>
@@ -14305,17 +14349,15 @@
         <v>104</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>426</v>
+        <v>459</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>427</v>
+        <v>460</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="O101" t="s" s="2">
-        <v>429</v>
-      </c>
+        <v>461</v>
+      </c>
+      <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
         <v>82</v>
       </c>
@@ -14363,13 +14405,13 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>430</v>
+        <v>462</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI101" t="s" s="2">
         <v>82</v>
@@ -14378,7 +14420,7 @@
         <v>102</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>431</v>
+        <v>463</v>
       </c>
       <c r="AL101" t="s" s="2">
         <v>82</v>
@@ -14387,7 +14429,7 @@
         <v>82</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>432</v>
+        <v>464</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>82</v>
@@ -14395,21 +14437,21 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>486</v>
+        <v>465</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>434</v>
+        <v>466</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
-        <v>435</v>
+        <v>82</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H102" t="s" s="2">
         <v>82</v>
@@ -14424,14 +14466,12 @@
         <v>104</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>436</v>
+        <v>467</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>438</v>
-      </c>
+        <v>468</v>
+      </c>
+      <c r="N102" s="2"/>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
         <v>82</v>
@@ -14480,13 +14520,13 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>439</v>
+        <v>469</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI102" t="s" s="2">
         <v>82</v>
@@ -14495,7 +14535,7 @@
         <v>102</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>440</v>
+        <v>470</v>
       </c>
       <c r="AL102" t="s" s="2">
         <v>82</v>
@@ -14504,7 +14544,7 @@
         <v>82</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>441</v>
+        <v>471</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>82</v>
@@ -14512,18 +14552,18 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>487</v>
+        <v>472</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>443</v>
+        <v>473</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
-        <v>444</v>
+        <v>82</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G103" t="s" s="2">
         <v>81</v>
@@ -14541,14 +14581,12 @@
         <v>104</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>445</v>
+        <v>474</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>447</v>
-      </c>
+        <v>475</v>
+      </c>
+      <c r="N103" s="2"/>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
         <v>82</v>
@@ -14597,7 +14635,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>448</v>
+        <v>476</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -14612,7 +14650,7 @@
         <v>102</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>449</v>
+        <v>477</v>
       </c>
       <c r="AL103" t="s" s="2">
         <v>82</v>
@@ -14621,7 +14659,7 @@
         <v>82</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>450</v>
+        <v>478</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>82</v>
@@ -14629,10 +14667,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>488</v>
+        <v>479</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>452</v>
+        <v>480</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14643,7 +14681,7 @@
         <v>80</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H104" t="s" s="2">
         <v>82</v>
@@ -14655,16 +14693,18 @@
         <v>91</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>104</v>
+        <v>303</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>453</v>
+        <v>481</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>454</v>
+        <v>482</v>
       </c>
       <c r="N104" s="2"/>
-      <c r="O104" s="2"/>
+      <c r="O104" t="s" s="2">
+        <v>483</v>
+      </c>
       <c r="P104" t="s" s="2">
         <v>82</v>
       </c>
@@ -14712,13 +14752,13 @@
         <v>82</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>455</v>
+        <v>484</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH104" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI104" t="s" s="2">
         <v>82</v>
@@ -14727,7 +14767,7 @@
         <v>102</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>456</v>
+        <v>485</v>
       </c>
       <c r="AL104" t="s" s="2">
         <v>82</v>
@@ -14736,7 +14776,7 @@
         <v>82</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>457</v>
+        <v>486</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>82</v>
@@ -14744,12 +14784,14 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="C105" s="2"/>
+        <v>407</v>
+      </c>
+      <c r="C105" t="s" s="2">
+        <v>488</v>
+      </c>
       <c r="D105" t="s" s="2">
         <v>82</v>
       </c>
@@ -14770,16 +14812,20 @@
         <v>91</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>104</v>
+        <v>419</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>460</v>
+        <v>489</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="N105" s="2"/>
-      <c r="O105" s="2"/>
+        <v>490</v>
+      </c>
+      <c r="N105" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="O105" t="s" s="2">
+        <v>412</v>
+      </c>
       <c r="P105" t="s" s="2">
         <v>82</v>
       </c>
@@ -14827,7 +14873,7 @@
         <v>82</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>462</v>
+        <v>407</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -14842,16 +14888,16 @@
         <v>102</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>463</v>
+        <v>414</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>82</v>
+        <v>415</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>464</v>
+        <v>416</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>82</v>
@@ -14859,10 +14905,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>466</v>
+        <v>423</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14882,21 +14928,19 @@
         <v>82</v>
       </c>
       <c r="J106" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>303</v>
+        <v>104</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>467</v>
+        <v>105</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>468</v>
+        <v>106</v>
       </c>
       <c r="N106" s="2"/>
-      <c r="O106" t="s" s="2">
-        <v>469</v>
-      </c>
+      <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
         <v>82</v>
       </c>
@@ -14944,7 +14988,7 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>470</v>
+        <v>107</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -14956,10 +15000,10 @@
         <v>82</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>471</v>
+        <v>108</v>
       </c>
       <c r="AL106" t="s" s="2">
         <v>82</v>
@@ -14968,7 +15012,7 @@
         <v>82</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>472</v>
+        <v>82</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>82</v>
@@ -14976,14 +15020,14 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>491</v>
+        <v>425</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
@@ -14999,23 +15043,21 @@
         <v>82</v>
       </c>
       <c r="J107" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>492</v>
+        <v>111</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>493</v>
+        <v>112</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>494</v>
+        <v>113</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="O107" t="s" s="2">
-        <v>496</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
         <v>82</v>
       </c>
@@ -15051,19 +15093,19 @@
         <v>82</v>
       </c>
       <c r="AB107" t="s" s="2">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="AC107" t="s" s="2">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="AD107" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE107" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>491</v>
+        <v>118</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -15075,19 +15117,19 @@
         <v>82</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>497</v>
+        <v>108</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>498</v>
+        <v>82</v>
       </c>
       <c r="AM107" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>499</v>
+        <v>82</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>82</v>
@@ -15095,12 +15137,14 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>500</v>
+        <v>493</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="C108" s="2"/>
+        <v>425</v>
+      </c>
+      <c r="C108" t="s" s="2">
+        <v>494</v>
+      </c>
       <c r="D108" t="s" s="2">
         <v>82</v>
       </c>
@@ -15118,23 +15162,19 @@
         <v>82</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>171</v>
+        <v>495</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="N108" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="O108" t="s" s="2">
-        <v>504</v>
-      </c>
+        <v>497</v>
+      </c>
+      <c r="N108" s="2"/>
+      <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
         <v>82</v>
       </c>
@@ -15158,11 +15198,13 @@
         <v>82</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="Y108" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y108" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z108" t="s" s="2">
-        <v>505</v>
+        <v>82</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>82</v>
@@ -15180,31 +15222,31 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>500</v>
+        <v>118</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH108" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI108" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>506</v>
+        <v>82</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>507</v>
+        <v>82</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>508</v>
+        <v>82</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>82</v>
@@ -15212,10 +15254,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>509</v>
+        <v>498</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>509</v>
+        <v>427</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15223,7 +15265,7 @@
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G109" t="s" s="2">
         <v>90</v>
@@ -15232,25 +15274,25 @@
         <v>82</v>
       </c>
       <c r="I109" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="J109" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>510</v>
+        <v>171</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>511</v>
+        <v>428</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>512</v>
+        <v>429</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>513</v>
+        <v>430</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>514</v>
+        <v>431</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>82</v>
@@ -15260,7 +15302,7 @@
         <v>82</v>
       </c>
       <c r="S109" t="s" s="2">
-        <v>82</v>
+        <v>323</v>
       </c>
       <c r="T109" t="s" s="2">
         <v>82</v>
@@ -15275,13 +15317,13 @@
         <v>82</v>
       </c>
       <c r="X109" t="s" s="2">
-        <v>82</v>
+        <v>271</v>
       </c>
       <c r="Y109" t="s" s="2">
-        <v>82</v>
+        <v>433</v>
       </c>
       <c r="Z109" t="s" s="2">
-        <v>82</v>
+        <v>434</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>82</v>
@@ -15299,7 +15341,7 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>509</v>
+        <v>435</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15314,27 +15356,27 @@
         <v>102</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>515</v>
+        <v>436</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>516</v>
+        <v>82</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>517</v>
+        <v>437</v>
       </c>
       <c r="AO109" t="s" s="2">
-        <v>518</v>
+        <v>82</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>519</v>
+        <v>499</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>519</v>
+        <v>439</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15351,25 +15393,25 @@
         <v>82</v>
       </c>
       <c r="I110" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J110" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>520</v>
+        <v>104</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>521</v>
+        <v>440</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>522</v>
+        <v>441</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>523</v>
+        <v>442</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>524</v>
+        <v>443</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>82</v>
@@ -15418,7 +15460,7 @@
         <v>82</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>519</v>
+        <v>444</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -15433,16 +15475,16 @@
         <v>102</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>525</v>
+        <v>445</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="AM110" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>526</v>
+        <v>446</v>
       </c>
       <c r="AO110" t="s" s="2">
         <v>82</v>
@@ -15450,21 +15492,21 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>527</v>
+        <v>500</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>527</v>
+        <v>448</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
-        <v>82</v>
+        <v>449</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G111" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H111" t="s" s="2">
         <v>82</v>
@@ -15476,20 +15518,18 @@
         <v>91</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>238</v>
+        <v>104</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>528</v>
+        <v>450</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>529</v>
+        <v>451</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="O111" t="s" s="2">
-        <v>531</v>
-      </c>
+        <v>452</v>
+      </c>
+      <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
         <v>82</v>
       </c>
@@ -15537,13 +15577,13 @@
         <v>82</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>527</v>
+        <v>453</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH111" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI111" t="s" s="2">
         <v>82</v>
@@ -15552,16 +15592,16 @@
         <v>102</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>532</v>
+        <v>454</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>533</v>
+        <v>82</v>
       </c>
       <c r="AM111" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>534</v>
+        <v>455</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>82</v>
@@ -15569,21 +15609,21 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>535</v>
+        <v>501</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>535</v>
+        <v>457</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
-        <v>82</v>
+        <v>458</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G112" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H112" t="s" s="2">
         <v>82</v>
@@ -15592,21 +15632,21 @@
         <v>82</v>
       </c>
       <c r="J112" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>277</v>
+        <v>104</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>536</v>
+        <v>459</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="N112" s="2"/>
-      <c r="O112" t="s" s="2">
-        <v>538</v>
-      </c>
+        <v>460</v>
+      </c>
+      <c r="N112" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
         <v>82</v>
       </c>
@@ -15630,11 +15670,13 @@
         <v>82</v>
       </c>
       <c r="X112" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="Y112" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y112" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z112" t="s" s="2">
-        <v>539</v>
+        <v>82</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>82</v>
@@ -15652,13 +15694,13 @@
         <v>82</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>535</v>
+        <v>462</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH112" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI112" t="s" s="2">
         <v>82</v>
@@ -15667,16 +15709,16 @@
         <v>102</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>540</v>
+        <v>463</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>541</v>
+        <v>82</v>
       </c>
       <c r="AM112" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>542</v>
+        <v>464</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>82</v>
@@ -15684,10 +15726,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>543</v>
+        <v>502</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>543</v>
+        <v>466</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15698,7 +15740,7 @@
         <v>80</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H113" t="s" s="2">
         <v>82</v>
@@ -15707,23 +15749,19 @@
         <v>82</v>
       </c>
       <c r="J113" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>544</v>
+        <v>104</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>545</v>
+        <v>467</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="N113" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="O113" t="s" s="2">
-        <v>548</v>
-      </c>
+        <v>468</v>
+      </c>
+      <c r="N113" s="2"/>
+      <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
         <v>82</v>
       </c>
@@ -15771,13 +15809,13 @@
         <v>82</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>543</v>
+        <v>469</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH113" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI113" t="s" s="2">
         <v>82</v>
@@ -15786,16 +15824,16 @@
         <v>102</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>549</v>
+        <v>470</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>550</v>
+        <v>471</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>82</v>
@@ -15803,10 +15841,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>551</v>
+        <v>503</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>551</v>
+        <v>473</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15826,23 +15864,19 @@
         <v>82</v>
       </c>
       <c r="J114" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>552</v>
+        <v>104</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>553</v>
+        <v>474</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>554</v>
-      </c>
-      <c r="N114" t="s" s="2">
-        <v>555</v>
-      </c>
-      <c r="O114" t="s" s="2">
-        <v>556</v>
-      </c>
+        <v>475</v>
+      </c>
+      <c r="N114" s="2"/>
+      <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
         <v>82</v>
       </c>
@@ -15890,7 +15924,7 @@
         <v>82</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>551</v>
+        <v>476</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -15905,16 +15939,16 @@
         <v>102</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>557</v>
+        <v>477</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="AM114" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>558</v>
+        <v>478</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>82</v>
@@ -15922,10 +15956,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>559</v>
+        <v>504</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>559</v>
+        <v>480</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15936,7 +15970,7 @@
         <v>80</v>
       </c>
       <c r="G115" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H115" t="s" s="2">
         <v>82</v>
@@ -15945,22 +15979,20 @@
         <v>82</v>
       </c>
       <c r="J115" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>560</v>
+        <v>303</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>561</v>
+        <v>481</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="N115" t="s" s="2">
-        <v>563</v>
-      </c>
+        <v>482</v>
+      </c>
+      <c r="N115" s="2"/>
       <c r="O115" t="s" s="2">
-        <v>564</v>
+        <v>483</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>82</v>
@@ -16009,31 +16041,31 @@
         <v>82</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>559</v>
+        <v>484</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH115" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI115" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>565</v>
+        <v>102</v>
       </c>
       <c r="AK115" t="s" s="2">
-        <v>566</v>
+        <v>485</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="AM115" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>82</v>
+        <v>486</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>82</v>
@@ -16041,10 +16073,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>567</v>
+        <v>505</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>567</v>
+        <v>505</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16055,7 +16087,7 @@
         <v>80</v>
       </c>
       <c r="G116" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H116" t="s" s="2">
         <v>82</v>
@@ -16064,19 +16096,23 @@
         <v>82</v>
       </c>
       <c r="J116" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>104</v>
+        <v>506</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>105</v>
+        <v>507</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N116" s="2"/>
-      <c r="O116" s="2"/>
+        <v>508</v>
+      </c>
+      <c r="N116" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="O116" t="s" s="2">
+        <v>510</v>
+      </c>
       <c r="P116" t="s" s="2">
         <v>82</v>
       </c>
@@ -16124,31 +16160,31 @@
         <v>82</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>107</v>
+        <v>505</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH116" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI116" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ116" t="s" s="2">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="AK116" t="s" s="2">
-        <v>108</v>
+        <v>511</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>82</v>
+        <v>512</v>
       </c>
       <c r="AM116" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>82</v>
+        <v>513</v>
       </c>
       <c r="AO116" t="s" s="2">
         <v>82</v>
@@ -16156,10 +16192,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>568</v>
+        <v>514</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>568</v>
+        <v>514</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16170,7 +16206,7 @@
         <v>80</v>
       </c>
       <c r="G117" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H117" t="s" s="2">
         <v>82</v>
@@ -16179,19 +16215,23 @@
         <v>82</v>
       </c>
       <c r="J117" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>111</v>
+        <v>171</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>196</v>
+        <v>515</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="N117" s="2"/>
-      <c r="O117" s="2"/>
+        <v>516</v>
+      </c>
+      <c r="N117" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="O117" t="s" s="2">
+        <v>518</v>
+      </c>
       <c r="P117" t="s" s="2">
         <v>82</v>
       </c>
@@ -16215,53 +16255,53 @@
         <v>82</v>
       </c>
       <c r="X117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y117" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="Y117" s="2"/>
       <c r="Z117" t="s" s="2">
-        <v>82</v>
+        <v>519</v>
       </c>
       <c r="AA117" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB117" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="AC117" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC117" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD117" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE117" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>118</v>
+        <v>514</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH117" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI117" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK117" t="s" s="2">
-        <v>82</v>
+        <v>520</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>82</v>
+        <v>521</v>
       </c>
       <c r="AM117" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN117" t="s" s="2">
-        <v>82</v>
+        <v>522</v>
       </c>
       <c r="AO117" t="s" s="2">
         <v>82</v>
@@ -16269,14 +16309,12 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>569</v>
+        <v>523</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>568</v>
-      </c>
-      <c r="C118" t="s" s="2">
-        <v>570</v>
-      </c>
+        <v>523</v>
+      </c>
+      <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
         <v>82</v>
       </c>
@@ -16294,19 +16332,23 @@
         <v>82</v>
       </c>
       <c r="J118" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>571</v>
+        <v>524</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>572</v>
+        <v>525</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="N118" s="2"/>
-      <c r="O118" s="2"/>
+        <v>526</v>
+      </c>
+      <c r="N118" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="O118" t="s" s="2">
+        <v>528</v>
+      </c>
       <c r="P118" t="s" s="2">
         <v>82</v>
       </c>
@@ -16354,46 +16396,44 @@
         <v>82</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>118</v>
+        <v>523</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH118" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI118" t="s" s="2">
-        <v>204</v>
+        <v>82</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK118" t="s" s="2">
-        <v>82</v>
+        <v>529</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>82</v>
+        <v>530</v>
       </c>
       <c r="AM118" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN118" t="s" s="2">
-        <v>82</v>
+        <v>531</v>
       </c>
       <c r="AO118" t="s" s="2">
-        <v>82</v>
+        <v>532</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>574</v>
+        <v>533</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>568</v>
-      </c>
-      <c r="C119" t="s" s="2">
-        <v>575</v>
-      </c>
+        <v>533</v>
+      </c>
+      <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
         <v>82</v>
       </c>
@@ -16408,22 +16448,26 @@
         <v>82</v>
       </c>
       <c r="I119" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="J119" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>576</v>
+        <v>534</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>577</v>
+        <v>535</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="N119" s="2"/>
-      <c r="O119" s="2"/>
+        <v>536</v>
+      </c>
+      <c r="N119" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="O119" t="s" s="2">
+        <v>538</v>
+      </c>
       <c r="P119" t="s" s="2">
         <v>82</v>
       </c>
@@ -16471,31 +16515,31 @@
         <v>82</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>118</v>
+        <v>533</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH119" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI119" t="s" s="2">
-        <v>204</v>
+        <v>82</v>
       </c>
       <c r="AJ119" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK119" t="s" s="2">
-        <v>82</v>
+        <v>539</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="AM119" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN119" t="s" s="2">
-        <v>82</v>
+        <v>540</v>
       </c>
       <c r="AO119" t="s" s="2">
         <v>82</v>
@@ -16503,14 +16547,14 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>579</v>
+        <v>541</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>579</v>
+        <v>541</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
-        <v>580</v>
+        <v>82</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
@@ -16523,25 +16567,25 @@
         <v>82</v>
       </c>
       <c r="I120" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J120" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>111</v>
+        <v>238</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>581</v>
+        <v>542</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>582</v>
+        <v>543</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>114</v>
+        <v>544</v>
       </c>
       <c r="O120" t="s" s="2">
-        <v>251</v>
+        <v>545</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>82</v>
@@ -16590,7 +16634,7 @@
         <v>82</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>583</v>
+        <v>541</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
@@ -16602,19 +16646,19 @@
         <v>82</v>
       </c>
       <c r="AJ120" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK120" t="s" s="2">
-        <v>194</v>
+        <v>546</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>82</v>
+        <v>547</v>
       </c>
       <c r="AM120" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN120" t="s" s="2">
-        <v>82</v>
+        <v>548</v>
       </c>
       <c r="AO120" t="s" s="2">
         <v>82</v>
@@ -16622,10 +16666,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>584</v>
+        <v>549</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>584</v>
+        <v>549</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16636,7 +16680,7 @@
         <v>80</v>
       </c>
       <c r="G121" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H121" t="s" s="2">
         <v>82</v>
@@ -16651,14 +16695,14 @@
         <v>277</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>585</v>
+        <v>550</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>586</v>
+        <v>551</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" t="s" s="2">
-        <v>587</v>
+        <v>552</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>82</v>
@@ -16685,33 +16729,33 @@
       <c r="X121" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="Y121" t="s" s="2">
-        <v>588</v>
-      </c>
+      <c r="Y121" s="2"/>
       <c r="Z121" t="s" s="2">
-        <v>589</v>
+        <v>553</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB121" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AC121" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC121" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD121" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE121" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>584</v>
+        <v>549</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH121" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI121" t="s" s="2">
         <v>82</v>
@@ -16720,16 +16764,16 @@
         <v>102</v>
       </c>
       <c r="AK121" t="s" s="2">
-        <v>590</v>
+        <v>554</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>108</v>
+        <v>555</v>
       </c>
       <c r="AM121" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>591</v>
+        <v>556</v>
       </c>
       <c r="AO121" t="s" s="2">
         <v>82</v>
@@ -16737,14 +16781,12 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>592</v>
+        <v>557</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="C122" t="s" s="2">
-        <v>593</v>
-      </c>
+        <v>557</v>
+      </c>
+      <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
         <v>82</v>
       </c>
@@ -16765,17 +16807,19 @@
         <v>82</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>277</v>
+        <v>558</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>594</v>
+        <v>559</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="N122" s="2"/>
+        <v>560</v>
+      </c>
+      <c r="N122" t="s" s="2">
+        <v>561</v>
+      </c>
       <c r="O122" t="s" s="2">
-        <v>587</v>
+        <v>562</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>82</v>
@@ -16800,11 +16844,13 @@
         <v>82</v>
       </c>
       <c r="X122" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="Y122" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y122" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z122" t="s" s="2">
-        <v>595</v>
+        <v>82</v>
       </c>
       <c r="AA122" t="s" s="2">
         <v>82</v>
@@ -16822,13 +16868,13 @@
         <v>82</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>584</v>
+        <v>557</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH122" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI122" t="s" s="2">
         <v>82</v>
@@ -16837,7 +16883,7 @@
         <v>102</v>
       </c>
       <c r="AK122" t="s" s="2">
-        <v>590</v>
+        <v>563</v>
       </c>
       <c r="AL122" t="s" s="2">
         <v>108</v>
@@ -16846,7 +16892,7 @@
         <v>82</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>591</v>
+        <v>564</v>
       </c>
       <c r="AO122" t="s" s="2">
         <v>82</v>
@@ -16854,14 +16900,12 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>596</v>
+        <v>565</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="C123" t="s" s="2">
-        <v>597</v>
-      </c>
+        <v>565</v>
+      </c>
+      <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
         <v>82</v>
       </c>
@@ -16870,7 +16914,7 @@
         <v>80</v>
       </c>
       <c r="G123" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H123" t="s" s="2">
         <v>82</v>
@@ -16882,17 +16926,19 @@
         <v>82</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>277</v>
+        <v>566</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>598</v>
+        <v>567</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="N123" s="2"/>
+        <v>568</v>
+      </c>
+      <c r="N123" t="s" s="2">
+        <v>569</v>
+      </c>
       <c r="O123" t="s" s="2">
-        <v>587</v>
+        <v>570</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>82</v>
@@ -16917,11 +16963,13 @@
         <v>82</v>
       </c>
       <c r="X123" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="Y123" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y123" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z123" t="s" s="2">
-        <v>599</v>
+        <v>82</v>
       </c>
       <c r="AA123" t="s" s="2">
         <v>82</v>
@@ -16939,7 +16987,7 @@
         <v>82</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>584</v>
+        <v>565</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
@@ -16954,7 +17002,7 @@
         <v>102</v>
       </c>
       <c r="AK123" t="s" s="2">
-        <v>590</v>
+        <v>571</v>
       </c>
       <c r="AL123" t="s" s="2">
         <v>108</v>
@@ -16963,7 +17011,7 @@
         <v>82</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>591</v>
+        <v>572</v>
       </c>
       <c r="AO123" t="s" s="2">
         <v>82</v>
@@ -16971,10 +17019,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>600</v>
+        <v>573</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>600</v>
+        <v>573</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16985,7 +17033,7 @@
         <v>80</v>
       </c>
       <c r="G124" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H124" t="s" s="2">
         <v>82</v>
@@ -16997,17 +17045,19 @@
         <v>82</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>394</v>
+        <v>574</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>601</v>
+        <v>575</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="N124" s="2"/>
+        <v>576</v>
+      </c>
+      <c r="N124" t="s" s="2">
+        <v>577</v>
+      </c>
       <c r="O124" t="s" s="2">
-        <v>603</v>
+        <v>578</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>82</v>
@@ -17056,22 +17106,22 @@
         <v>82</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>600</v>
+        <v>573</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH124" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI124" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ124" t="s" s="2">
-        <v>102</v>
+        <v>579</v>
       </c>
       <c r="AK124" t="s" s="2">
-        <v>400</v>
+        <v>580</v>
       </c>
       <c r="AL124" t="s" s="2">
         <v>108</v>
@@ -17080,7 +17130,7 @@
         <v>82</v>
       </c>
       <c r="AN124" t="s" s="2">
-        <v>604</v>
+        <v>82</v>
       </c>
       <c r="AO124" t="s" s="2">
         <v>82</v>
@@ -17088,10 +17138,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>605</v>
+        <v>581</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>605</v>
+        <v>581</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17102,7 +17152,7 @@
         <v>80</v>
       </c>
       <c r="G125" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H125" t="s" s="2">
         <v>82</v>
@@ -17114,20 +17164,16 @@
         <v>82</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>492</v>
+        <v>104</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>606</v>
+        <v>105</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>607</v>
-      </c>
-      <c r="N125" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="O125" t="s" s="2">
-        <v>496</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N125" s="2"/>
+      <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
         <v>82</v>
       </c>
@@ -17175,31 +17221,31 @@
         <v>82</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>605</v>
+        <v>107</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH125" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI125" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ125" t="s" s="2">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="AK125" t="s" s="2">
-        <v>497</v>
+        <v>108</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="AM125" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN125" t="s" s="2">
-        <v>609</v>
+        <v>82</v>
       </c>
       <c r="AO125" t="s" s="2">
         <v>82</v>
@@ -17207,10 +17253,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>610</v>
+        <v>582</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>610</v>
+        <v>582</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17221,7 +17267,7 @@
         <v>80</v>
       </c>
       <c r="G126" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H126" t="s" s="2">
         <v>82</v>
@@ -17233,18 +17279,16 @@
         <v>82</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>611</v>
+        <v>111</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>612</v>
+        <v>196</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>613</v>
+        <v>197</v>
       </c>
       <c r="N126" s="2"/>
-      <c r="O126" t="s" s="2">
-        <v>614</v>
-      </c>
+      <c r="O126" s="2"/>
       <c r="P126" t="s" s="2">
         <v>82</v>
       </c>
@@ -17280,43 +17324,41 @@
         <v>82</v>
       </c>
       <c r="AB126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC126" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="AC126" s="2"/>
       <c r="AD126" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE126" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>610</v>
+        <v>118</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH126" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI126" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ126" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK126" t="s" s="2">
-        <v>532</v>
+        <v>82</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="AM126" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN126" t="s" s="2">
-        <v>615</v>
+        <v>82</v>
       </c>
       <c r="AO126" t="s" s="2">
         <v>82</v>
@@ -17324,12 +17366,14 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>616</v>
+        <v>583</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>616</v>
-      </c>
-      <c r="C127" s="2"/>
+        <v>582</v>
+      </c>
+      <c r="C127" t="s" s="2">
+        <v>584</v>
+      </c>
       <c r="D127" t="s" s="2">
         <v>82</v>
       </c>
@@ -17350,18 +17394,16 @@
         <v>82</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>171</v>
+        <v>585</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>617</v>
+        <v>586</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>618</v>
+        <v>587</v>
       </c>
       <c r="N127" s="2"/>
-      <c r="O127" t="s" s="2">
-        <v>619</v>
-      </c>
+      <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
         <v>82</v>
       </c>
@@ -17385,13 +17427,13 @@
         <v>82</v>
       </c>
       <c r="X127" t="s" s="2">
-        <v>271</v>
+        <v>82</v>
       </c>
       <c r="Y127" t="s" s="2">
-        <v>620</v>
+        <v>82</v>
       </c>
       <c r="Z127" t="s" s="2">
-        <v>621</v>
+        <v>82</v>
       </c>
       <c r="AA127" t="s" s="2">
         <v>82</v>
@@ -17409,31 +17451,31 @@
         <v>82</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>616</v>
+        <v>118</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH127" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI127" t="s" s="2">
-        <v>82</v>
+        <v>204</v>
       </c>
       <c r="AJ127" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK127" t="s" s="2">
-        <v>506</v>
+        <v>82</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="AM127" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN127" t="s" s="2">
-        <v>622</v>
+        <v>82</v>
       </c>
       <c r="AO127" t="s" s="2">
         <v>82</v>
@@ -17441,12 +17483,14 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>623</v>
+        <v>588</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>623</v>
-      </c>
-      <c r="C128" s="2"/>
+        <v>582</v>
+      </c>
+      <c r="C128" t="s" s="2">
+        <v>589</v>
+      </c>
       <c r="D128" t="s" s="2">
         <v>82</v>
       </c>
@@ -17467,18 +17511,16 @@
         <v>82</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>310</v>
+        <v>590</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>624</v>
+        <v>591</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>625</v>
+        <v>592</v>
       </c>
       <c r="N128" s="2"/>
-      <c r="O128" t="s" s="2">
-        <v>626</v>
-      </c>
+      <c r="O128" s="2"/>
       <c r="P128" t="s" s="2">
         <v>82</v>
       </c>
@@ -17526,31 +17568,31 @@
         <v>82</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>623</v>
+        <v>118</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH128" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI128" t="s" s="2">
-        <v>627</v>
+        <v>204</v>
       </c>
       <c r="AJ128" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK128" t="s" s="2">
-        <v>628</v>
+        <v>82</v>
       </c>
       <c r="AL128" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="AM128" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN128" t="s" s="2">
-        <v>629</v>
+        <v>82</v>
       </c>
       <c r="AO128" t="s" s="2">
         <v>82</v>
@@ -17558,42 +17600,46 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>630</v>
+        <v>593</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>630</v>
+        <v>593</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
-        <v>82</v>
+        <v>594</v>
       </c>
       <c r="E129" s="2"/>
       <c r="F129" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G129" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H129" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I129" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="J129" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>303</v>
+        <v>111</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>631</v>
+        <v>595</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>632</v>
-      </c>
-      <c r="N129" s="2"/>
-      <c r="O129" s="2"/>
+        <v>596</v>
+      </c>
+      <c r="N129" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O129" t="s" s="2">
+        <v>251</v>
+      </c>
       <c r="P129" t="s" s="2">
         <v>82</v>
       </c>
@@ -17641,25 +17687,25 @@
         <v>82</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>630</v>
+        <v>597</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH129" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI129" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ129" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK129" t="s" s="2">
-        <v>633</v>
+        <v>194</v>
       </c>
       <c r="AL129" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="AM129" t="s" s="2">
         <v>82</v>
@@ -17673,10 +17719,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>634</v>
+        <v>598</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>634</v>
+        <v>598</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17699,19 +17745,17 @@
         <v>82</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>560</v>
+        <v>277</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>635</v>
+        <v>599</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>636</v>
-      </c>
-      <c r="N130" t="s" s="2">
-        <v>637</v>
-      </c>
+        <v>600</v>
+      </c>
+      <c r="N130" s="2"/>
       <c r="O130" t="s" s="2">
-        <v>638</v>
+        <v>601</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>82</v>
@@ -17736,31 +17780,29 @@
         <v>82</v>
       </c>
       <c r="X130" t="s" s="2">
-        <v>82</v>
+        <v>153</v>
       </c>
       <c r="Y130" t="s" s="2">
-        <v>82</v>
+        <v>602</v>
       </c>
       <c r="Z130" t="s" s="2">
-        <v>82</v>
+        <v>603</v>
       </c>
       <c r="AA130" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB130" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC130" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="AC130" s="2"/>
       <c r="AD130" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE130" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>634</v>
+        <v>598</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>80</v>
@@ -17775,16 +17817,16 @@
         <v>102</v>
       </c>
       <c r="AK130" t="s" s="2">
-        <v>639</v>
+        <v>604</v>
       </c>
       <c r="AL130" t="s" s="2">
-        <v>640</v>
+        <v>108</v>
       </c>
       <c r="AM130" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN130" t="s" s="2">
-        <v>82</v>
+        <v>605</v>
       </c>
       <c r="AO130" t="s" s="2">
         <v>82</v>
@@ -17792,12 +17834,14 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>641</v>
+        <v>606</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>641</v>
-      </c>
-      <c r="C131" s="2"/>
+        <v>598</v>
+      </c>
+      <c r="C131" t="s" s="2">
+        <v>607</v>
+      </c>
       <c r="D131" t="s" s="2">
         <v>82</v>
       </c>
@@ -17818,16 +17862,18 @@
         <v>82</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>104</v>
+        <v>277</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>105</v>
+        <v>608</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>106</v>
+        <v>600</v>
       </c>
       <c r="N131" s="2"/>
-      <c r="O131" s="2"/>
+      <c r="O131" t="s" s="2">
+        <v>601</v>
+      </c>
       <c r="P131" t="s" s="2">
         <v>82</v>
       </c>
@@ -17851,13 +17897,11 @@
         <v>82</v>
       </c>
       <c r="X131" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y131" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="Y131" s="2"/>
       <c r="Z131" t="s" s="2">
-        <v>82</v>
+        <v>609</v>
       </c>
       <c r="AA131" t="s" s="2">
         <v>82</v>
@@ -17875,31 +17919,31 @@
         <v>82</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>107</v>
+        <v>598</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH131" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI131" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ131" t="s" s="2">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="AK131" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="AL131" t="s" s="2">
         <v>108</v>
       </c>
-      <c r="AL131" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AM131" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN131" t="s" s="2">
-        <v>82</v>
+        <v>605</v>
       </c>
       <c r="AO131" t="s" s="2">
         <v>82</v>
@@ -17907,21 +17951,23 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>642</v>
+        <v>610</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>642</v>
-      </c>
-      <c r="C132" s="2"/>
+        <v>598</v>
+      </c>
+      <c r="C132" t="s" s="2">
+        <v>611</v>
+      </c>
       <c r="D132" t="s" s="2">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="E132" s="2"/>
       <c r="F132" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G132" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H132" t="s" s="2">
         <v>82</v>
@@ -17933,18 +17979,18 @@
         <v>82</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>111</v>
+        <v>277</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>112</v>
+        <v>612</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N132" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O132" s="2"/>
+        <v>600</v>
+      </c>
+      <c r="N132" s="2"/>
+      <c r="O132" t="s" s="2">
+        <v>601</v>
+      </c>
       <c r="P132" t="s" s="2">
         <v>82</v>
       </c>
@@ -17968,13 +18014,11 @@
         <v>82</v>
       </c>
       <c r="X132" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y132" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="Y132" s="2"/>
       <c r="Z132" t="s" s="2">
-        <v>82</v>
+        <v>613</v>
       </c>
       <c r="AA132" t="s" s="2">
         <v>82</v>
@@ -17992,7 +18036,7 @@
         <v>82</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>118</v>
+        <v>598</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
@@ -18004,19 +18048,19 @@
         <v>82</v>
       </c>
       <c r="AJ132" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK132" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="AL132" t="s" s="2">
         <v>108</v>
       </c>
-      <c r="AL132" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AM132" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN132" t="s" s="2">
-        <v>82</v>
+        <v>605</v>
       </c>
       <c r="AO132" t="s" s="2">
         <v>82</v>
@@ -18024,45 +18068,43 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>643</v>
+        <v>614</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>643</v>
+        <v>614</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
-        <v>580</v>
+        <v>82</v>
       </c>
       <c r="E133" s="2"/>
       <c r="F133" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G133" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H133" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I133" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J133" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>111</v>
+        <v>408</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>581</v>
+        <v>615</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="N133" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>616</v>
+      </c>
+      <c r="N133" s="2"/>
       <c r="O133" t="s" s="2">
-        <v>251</v>
+        <v>617</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>82</v>
@@ -18111,31 +18153,31 @@
         <v>82</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>583</v>
+        <v>614</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH133" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI133" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ133" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK133" t="s" s="2">
-        <v>194</v>
+        <v>414</v>
       </c>
       <c r="AL133" t="s" s="2">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="AM133" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN133" t="s" s="2">
-        <v>82</v>
+        <v>618</v>
       </c>
       <c r="AO133" t="s" s="2">
         <v>82</v>
@@ -18143,10 +18185,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>644</v>
+        <v>619</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>644</v>
+        <v>619</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18154,10 +18196,10 @@
       </c>
       <c r="E134" s="2"/>
       <c r="F134" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G134" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H134" t="s" s="2">
         <v>82</v>
@@ -18169,19 +18211,19 @@
         <v>82</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>277</v>
+        <v>506</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>645</v>
+        <v>620</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>646</v>
+        <v>621</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>647</v>
+        <v>622</v>
       </c>
       <c r="O134" t="s" s="2">
-        <v>648</v>
+        <v>510</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>82</v>
@@ -18206,13 +18248,13 @@
         <v>82</v>
       </c>
       <c r="X134" t="s" s="2">
-        <v>175</v>
+        <v>82</v>
       </c>
       <c r="Y134" t="s" s="2">
-        <v>176</v>
+        <v>82</v>
       </c>
       <c r="Z134" t="s" s="2">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="AA134" t="s" s="2">
         <v>82</v>
@@ -18230,13 +18272,13 @@
         <v>82</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>644</v>
+        <v>619</v>
       </c>
       <c r="AG134" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH134" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI134" t="s" s="2">
         <v>82</v>
@@ -18245,16 +18287,16 @@
         <v>102</v>
       </c>
       <c r="AK134" t="s" s="2">
-        <v>649</v>
+        <v>511</v>
       </c>
       <c r="AL134" t="s" s="2">
-        <v>650</v>
+        <v>108</v>
       </c>
       <c r="AM134" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN134" t="s" s="2">
-        <v>651</v>
+        <v>623</v>
       </c>
       <c r="AO134" t="s" s="2">
         <v>82</v>
@@ -18262,10 +18304,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>652</v>
+        <v>624</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>652</v>
+        <v>624</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18288,19 +18330,17 @@
         <v>82</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>385</v>
+        <v>625</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>653</v>
+        <v>626</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>654</v>
-      </c>
-      <c r="N135" t="s" s="2">
-        <v>655</v>
-      </c>
+        <v>627</v>
+      </c>
+      <c r="N135" s="2"/>
       <c r="O135" t="s" s="2">
-        <v>656</v>
+        <v>628</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>82</v>
@@ -18349,7 +18389,7 @@
         <v>82</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>652</v>
+        <v>624</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>80</v>
@@ -18364,16 +18404,16 @@
         <v>102</v>
       </c>
       <c r="AK135" t="s" s="2">
-        <v>657</v>
+        <v>546</v>
       </c>
       <c r="AL135" t="s" s="2">
-        <v>658</v>
+        <v>108</v>
       </c>
       <c r="AM135" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN135" t="s" s="2">
-        <v>659</v>
+        <v>629</v>
       </c>
       <c r="AO135" t="s" s="2">
         <v>82</v>
@@ -18381,21 +18421,21 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>660</v>
+        <v>630</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>660</v>
+        <v>630</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
-        <v>661</v>
+        <v>82</v>
       </c>
       <c r="E136" s="2"/>
       <c r="F136" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G136" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H136" t="s" s="2">
         <v>82</v>
@@ -18407,18 +18447,18 @@
         <v>82</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>662</v>
+        <v>171</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>663</v>
+        <v>631</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>664</v>
-      </c>
-      <c r="N136" t="s" s="2">
-        <v>665</v>
-      </c>
-      <c r="O136" s="2"/>
+        <v>632</v>
+      </c>
+      <c r="N136" s="2"/>
+      <c r="O136" t="s" s="2">
+        <v>633</v>
+      </c>
       <c r="P136" t="s" s="2">
         <v>82</v>
       </c>
@@ -18442,13 +18482,13 @@
         <v>82</v>
       </c>
       <c r="X136" t="s" s="2">
-        <v>82</v>
+        <v>271</v>
       </c>
       <c r="Y136" t="s" s="2">
-        <v>82</v>
+        <v>634</v>
       </c>
       <c r="Z136" t="s" s="2">
-        <v>82</v>
+        <v>635</v>
       </c>
       <c r="AA136" t="s" s="2">
         <v>82</v>
@@ -18466,13 +18506,13 @@
         <v>82</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>660</v>
+        <v>630</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH136" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI136" t="s" s="2">
         <v>82</v>
@@ -18481,7 +18521,7 @@
         <v>102</v>
       </c>
       <c r="AK136" t="s" s="2">
-        <v>666</v>
+        <v>520</v>
       </c>
       <c r="AL136" t="s" s="2">
         <v>108</v>
@@ -18490,7 +18530,7 @@
         <v>82</v>
       </c>
       <c r="AN136" t="s" s="2">
-        <v>667</v>
+        <v>636</v>
       </c>
       <c r="AO136" t="s" s="2">
         <v>82</v>
@@ -18498,10 +18538,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>668</v>
+        <v>637</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>668</v>
+        <v>637</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18521,22 +18561,20 @@
         <v>82</v>
       </c>
       <c r="J137" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>669</v>
+        <v>310</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>670</v>
+        <v>638</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>671</v>
-      </c>
-      <c r="N137" t="s" s="2">
-        <v>672</v>
-      </c>
+        <v>639</v>
+      </c>
+      <c r="N137" s="2"/>
       <c r="O137" t="s" s="2">
-        <v>673</v>
+        <v>640</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>82</v>
@@ -18585,7 +18623,7 @@
         <v>82</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>668</v>
+        <v>637</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
@@ -18594,22 +18632,22 @@
         <v>90</v>
       </c>
       <c r="AI137" t="s" s="2">
-        <v>82</v>
+        <v>641</v>
       </c>
       <c r="AJ137" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK137" t="s" s="2">
-        <v>628</v>
+        <v>642</v>
       </c>
       <c r="AL137" t="s" s="2">
-        <v>674</v>
+        <v>108</v>
       </c>
       <c r="AM137" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN137" t="s" s="2">
-        <v>82</v>
+        <v>643</v>
       </c>
       <c r="AO137" t="s" s="2">
         <v>82</v>
@@ -18617,10 +18655,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>675</v>
+        <v>644</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>675</v>
+        <v>644</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -18631,32 +18669,28 @@
         <v>80</v>
       </c>
       <c r="G138" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H138" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I138" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J138" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>560</v>
+        <v>303</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>676</v>
+        <v>645</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>677</v>
-      </c>
-      <c r="N138" t="s" s="2">
-        <v>678</v>
-      </c>
-      <c r="O138" t="s" s="2">
-        <v>679</v>
-      </c>
+        <v>646</v>
+      </c>
+      <c r="N138" s="2"/>
+      <c r="O138" s="2"/>
       <c r="P138" t="s" s="2">
         <v>82</v>
       </c>
@@ -18704,13 +18738,13 @@
         <v>82</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>675</v>
+        <v>644</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH138" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI138" t="s" s="2">
         <v>82</v>
@@ -18719,7 +18753,7 @@
         <v>102</v>
       </c>
       <c r="AK138" t="s" s="2">
-        <v>680</v>
+        <v>647</v>
       </c>
       <c r="AL138" t="s" s="2">
         <v>108</v>
@@ -18736,10 +18770,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>681</v>
+        <v>648</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>681</v>
+        <v>648</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18750,7 +18784,7 @@
         <v>80</v>
       </c>
       <c r="G139" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H139" t="s" s="2">
         <v>82</v>
@@ -18762,16 +18796,20 @@
         <v>82</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>104</v>
+        <v>574</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>105</v>
+        <v>649</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N139" s="2"/>
-      <c r="O139" s="2"/>
+        <v>650</v>
+      </c>
+      <c r="N139" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="O139" t="s" s="2">
+        <v>652</v>
+      </c>
       <c r="P139" t="s" s="2">
         <v>82</v>
       </c>
@@ -18819,25 +18857,25 @@
         <v>82</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>107</v>
+        <v>648</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH139" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI139" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ139" t="s" s="2">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="AK139" t="s" s="2">
-        <v>108</v>
+        <v>653</v>
       </c>
       <c r="AL139" t="s" s="2">
-        <v>82</v>
+        <v>654</v>
       </c>
       <c r="AM139" t="s" s="2">
         <v>82</v>
@@ -18851,21 +18889,21 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>682</v>
+        <v>655</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>682</v>
+        <v>655</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="E140" s="2"/>
       <c r="F140" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G140" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H140" t="s" s="2">
         <v>82</v>
@@ -18877,17 +18915,15 @@
         <v>82</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N140" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N140" s="2"/>
       <c r="O140" s="2"/>
       <c r="P140" t="s" s="2">
         <v>82</v>
@@ -18936,19 +18972,19 @@
         <v>82</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH140" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI140" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ140" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AK140" t="s" s="2">
         <v>108</v>
@@ -18968,14 +19004,14 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>683</v>
+        <v>656</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>683</v>
+        <v>656</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
-        <v>580</v>
+        <v>110</v>
       </c>
       <c r="E141" s="2"/>
       <c r="F141" t="s" s="2">
@@ -18988,26 +19024,24 @@
         <v>82</v>
       </c>
       <c r="I141" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J141" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K141" t="s" s="2">
         <v>111</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>581</v>
+        <v>112</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>582</v>
+        <v>113</v>
       </c>
       <c r="N141" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="O141" t="s" s="2">
-        <v>251</v>
-      </c>
+      <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
         <v>82</v>
       </c>
@@ -19055,7 +19089,7 @@
         <v>82</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>583</v>
+        <v>118</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>80</v>
@@ -19070,7 +19104,7 @@
         <v>119</v>
       </c>
       <c r="AK141" t="s" s="2">
-        <v>194</v>
+        <v>108</v>
       </c>
       <c r="AL141" t="s" s="2">
         <v>82</v>
@@ -19087,44 +19121,46 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>684</v>
+        <v>657</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>684</v>
+        <v>657</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
-        <v>82</v>
+        <v>594</v>
       </c>
       <c r="E142" s="2"/>
       <c r="F142" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G142" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H142" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I142" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="J142" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>685</v>
+        <v>111</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>686</v>
+        <v>595</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>687</v>
+        <v>596</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>688</v>
-      </c>
-      <c r="O142" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="O142" t="s" s="2">
+        <v>251</v>
+      </c>
       <c r="P142" t="s" s="2">
         <v>82</v>
       </c>
@@ -19172,31 +19208,31 @@
         <v>82</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>684</v>
+        <v>597</v>
       </c>
       <c r="AG142" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH142" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI142" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ142" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK142" t="s" s="2">
-        <v>260</v>
+        <v>194</v>
       </c>
       <c r="AL142" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="AM142" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN142" t="s" s="2">
-        <v>689</v>
+        <v>82</v>
       </c>
       <c r="AO142" t="s" s="2">
         <v>82</v>
@@ -19204,10 +19240,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>690</v>
+        <v>658</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>690</v>
+        <v>658</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19227,19 +19263,23 @@
         <v>82</v>
       </c>
       <c r="J143" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>171</v>
+        <v>277</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>691</v>
+        <v>659</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>692</v>
-      </c>
-      <c r="N143" s="2"/>
-      <c r="O143" s="2"/>
+        <v>660</v>
+      </c>
+      <c r="N143" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="O143" t="s" s="2">
+        <v>662</v>
+      </c>
       <c r="P143" t="s" s="2">
         <v>82</v>
       </c>
@@ -19263,13 +19303,13 @@
         <v>82</v>
       </c>
       <c r="X143" t="s" s="2">
-        <v>271</v>
+        <v>175</v>
       </c>
       <c r="Y143" t="s" s="2">
-        <v>692</v>
+        <v>176</v>
       </c>
       <c r="Z143" t="s" s="2">
-        <v>693</v>
+        <v>177</v>
       </c>
       <c r="AA143" t="s" s="2">
         <v>82</v>
@@ -19287,7 +19327,7 @@
         <v>82</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>690</v>
+        <v>658</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>90</v>
@@ -19302,18 +19342,1075 @@
         <v>102</v>
       </c>
       <c r="AK143" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="AL143" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="AM143" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN143" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="AO143" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="B144" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="C144" s="2"/>
+      <c r="D144" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E144" s="2"/>
+      <c r="F144" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G144" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H144" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I144" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J144" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K144" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="L144" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="M144" t="s" s="2">
+        <v>668</v>
+      </c>
+      <c r="N144" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="O144" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="P144" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q144" s="2"/>
+      <c r="R144" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S144" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T144" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U144" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V144" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W144" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X144" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y144" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z144" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA144" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB144" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC144" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD144" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE144" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF144" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="AG144" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH144" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI144" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ144" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK144" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="AL144" t="s" s="2">
+        <v>672</v>
+      </c>
+      <c r="AM144" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN144" t="s" s="2">
+        <v>673</v>
+      </c>
+      <c r="AO144" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s" s="2">
+        <v>674</v>
+      </c>
+      <c r="B145" t="s" s="2">
+        <v>674</v>
+      </c>
+      <c r="C145" s="2"/>
+      <c r="D145" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="E145" s="2"/>
+      <c r="F145" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G145" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H145" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I145" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J145" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K145" t="s" s="2">
+        <v>676</v>
+      </c>
+      <c r="L145" t="s" s="2">
+        <v>677</v>
+      </c>
+      <c r="M145" t="s" s="2">
+        <v>678</v>
+      </c>
+      <c r="N145" t="s" s="2">
+        <v>679</v>
+      </c>
+      <c r="O145" s="2"/>
+      <c r="P145" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q145" s="2"/>
+      <c r="R145" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S145" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T145" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U145" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V145" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W145" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X145" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y145" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z145" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA145" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB145" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC145" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD145" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE145" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF145" t="s" s="2">
+        <v>674</v>
+      </c>
+      <c r="AG145" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH145" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI145" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ145" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK145" t="s" s="2">
+        <v>680</v>
+      </c>
+      <c r="AL145" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AM145" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN145" t="s" s="2">
+        <v>681</v>
+      </c>
+      <c r="AO145" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s" s="2">
+        <v>682</v>
+      </c>
+      <c r="B146" t="s" s="2">
+        <v>682</v>
+      </c>
+      <c r="C146" s="2"/>
+      <c r="D146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E146" s="2"/>
+      <c r="F146" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G146" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J146" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K146" t="s" s="2">
+        <v>683</v>
+      </c>
+      <c r="L146" t="s" s="2">
+        <v>684</v>
+      </c>
+      <c r="M146" t="s" s="2">
+        <v>685</v>
+      </c>
+      <c r="N146" t="s" s="2">
+        <v>686</v>
+      </c>
+      <c r="O146" t="s" s="2">
+        <v>687</v>
+      </c>
+      <c r="P146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q146" s="2"/>
+      <c r="R146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF146" t="s" s="2">
+        <v>682</v>
+      </c>
+      <c r="AG146" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH146" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ146" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK146" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="AL146" t="s" s="2">
+        <v>688</v>
+      </c>
+      <c r="AM146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO146" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s" s="2">
+        <v>689</v>
+      </c>
+      <c r="B147" t="s" s="2">
+        <v>689</v>
+      </c>
+      <c r="C147" s="2"/>
+      <c r="D147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E147" s="2"/>
+      <c r="F147" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G147" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I147" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="J147" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K147" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="L147" t="s" s="2">
+        <v>690</v>
+      </c>
+      <c r="M147" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="N147" t="s" s="2">
+        <v>692</v>
+      </c>
+      <c r="O147" t="s" s="2">
+        <v>693</v>
+      </c>
+      <c r="P147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q147" s="2"/>
+      <c r="R147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF147" t="s" s="2">
+        <v>689</v>
+      </c>
+      <c r="AG147" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH147" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ147" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK147" t="s" s="2">
         <v>694</v>
       </c>
-      <c r="AL143" t="s" s="2">
+      <c r="AL147" t="s" s="2">
         <v>108</v>
       </c>
-      <c r="AM143" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN143" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO143" t="s" s="2">
+      <c r="AM147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN147" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO147" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s" s="2">
+        <v>695</v>
+      </c>
+      <c r="B148" t="s" s="2">
+        <v>695</v>
+      </c>
+      <c r="C148" s="2"/>
+      <c r="D148" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E148" s="2"/>
+      <c r="F148" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G148" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H148" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I148" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J148" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K148" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L148" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="M148" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="N148" s="2"/>
+      <c r="O148" s="2"/>
+      <c r="P148" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q148" s="2"/>
+      <c r="R148" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S148" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T148" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U148" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V148" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W148" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X148" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y148" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z148" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA148" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB148" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC148" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD148" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE148" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF148" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AG148" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH148" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI148" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ148" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK148" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AL148" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM148" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN148" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO148" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s" s="2">
+        <v>696</v>
+      </c>
+      <c r="B149" t="s" s="2">
+        <v>696</v>
+      </c>
+      <c r="C149" s="2"/>
+      <c r="D149" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="E149" s="2"/>
+      <c r="F149" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G149" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K149" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L149" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="M149" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="N149" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O149" s="2"/>
+      <c r="P149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q149" s="2"/>
+      <c r="R149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF149" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AG149" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH149" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ149" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK149" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AL149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN149" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO149" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="B150" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="C150" s="2"/>
+      <c r="D150" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="E150" s="2"/>
+      <c r="F150" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G150" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I150" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="J150" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K150" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L150" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="M150" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="N150" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O150" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="P150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q150" s="2"/>
+      <c r="R150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF150" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="AG150" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH150" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ150" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK150" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="AL150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN150" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO150" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s" s="2">
+        <v>698</v>
+      </c>
+      <c r="B151" t="s" s="2">
+        <v>698</v>
+      </c>
+      <c r="C151" s="2"/>
+      <c r="D151" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E151" s="2"/>
+      <c r="F151" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G151" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H151" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I151" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J151" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K151" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="L151" t="s" s="2">
+        <v>700</v>
+      </c>
+      <c r="M151" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="N151" t="s" s="2">
+        <v>702</v>
+      </c>
+      <c r="O151" s="2"/>
+      <c r="P151" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q151" s="2"/>
+      <c r="R151" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S151" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T151" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U151" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V151" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W151" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X151" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y151" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z151" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA151" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB151" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC151" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD151" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE151" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF151" t="s" s="2">
+        <v>698</v>
+      </c>
+      <c r="AG151" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH151" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI151" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ151" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK151" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="AL151" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AM151" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN151" t="s" s="2">
+        <v>703</v>
+      </c>
+      <c r="AO151" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s" s="2">
+        <v>704</v>
+      </c>
+      <c r="B152" t="s" s="2">
+        <v>704</v>
+      </c>
+      <c r="C152" s="2"/>
+      <c r="D152" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E152" s="2"/>
+      <c r="F152" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G152" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H152" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I152" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J152" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K152" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L152" t="s" s="2">
+        <v>705</v>
+      </c>
+      <c r="M152" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="N152" s="2"/>
+      <c r="O152" s="2"/>
+      <c r="P152" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q152" s="2"/>
+      <c r="R152" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S152" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T152" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U152" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V152" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W152" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X152" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="Y152" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="Z152" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="AA152" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB152" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC152" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD152" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE152" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF152" t="s" s="2">
+        <v>704</v>
+      </c>
+      <c r="AG152" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH152" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI152" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ152" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK152" t="s" s="2">
+        <v>708</v>
+      </c>
+      <c r="AL152" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AM152" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN152" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO152" t="s" s="2">
         <v>82</v>
       </c>
     </row>
